--- a/performance_tracking_forms/020_youth_officers_performance_evaluation--performance_tracking_forms.xlsx
+++ b/performance_tracking_forms/020_youth_officers_performance_evaluation--performance_tracking_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,13 +437,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="47" customWidth="1" min="2" max="2"/>
-    <col width="39" customWidth="1" min="3" max="3"/>
-    <col width="6" customWidth="1" min="4" max="4"/>
+    <col width="29" customWidth="1" min="2" max="2"/>
+    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="24" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
@@ -515,23 +515,27 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>youth_officers_performance_evaluation_page_1</t>
+          <t>communication_skills</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Youth Officers Performance Evaluation</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr"/>
+          <t>How would you rate the youth officer's communication skills?</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Rate on a scale of 1-5</t>
+        </is>
+      </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -543,15 +547,19 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>youth_officers_performance_evaluation_page_2</t>
+          <t>leadership_skills</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Select One</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr"/>
+          <t>How would you rate the youth officer's leadership skills?</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Rate on a scale of 1-5</t>
+        </is>
+      </c>
       <c r="E5" t="inlineStr">
         <is>
           <t>yes</t>
@@ -561,23 +569,27 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>youth_officers_performance_evaluation_page_3</t>
+          <t>attendance_record</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Select Multiple</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr"/>
+          <t>What is the youth officer's average attendance record?</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Enter as number</t>
+        </is>
+      </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
     </row>
@@ -589,15 +601,19 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>youth_officers_performance_evaluation_page_4</t>
+          <t>last_meeting</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Date</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr"/>
+          <t>When was the last time the youth officer attended a staff meeting?</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Enter date</t>
+        </is>
+      </c>
       <c r="E7" t="inlineStr">
         <is>
           <t>no</t>
@@ -612,15 +628,19 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>youth_officers_performance_evaluation_page_5</t>
+          <t>start_time</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Time</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr"/>
+          <t>What is the youth officer's average start time for work each day?</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Enter time</t>
+        </is>
+      </c>
       <c r="E8" t="inlineStr">
         <is>
           <t>no</t>
@@ -630,23 +650,27 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>youth_officers_performance_evaluation_page_6</t>
+          <t>report_submission</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Text</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr"/>
+          <t>How well do you rate the youth officer's ability to write and submit reports on time?</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Select all that apply</t>
+        </is>
+      </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -658,15 +682,19 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>youth_officers_performance_evaluation_page_7</t>
+          <t>extra_hours</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Integer</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr"/>
+          <t>What is the number of hours spent on tasks outside of work hours to help with work-related tasks?</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Enter number</t>
+        </is>
+      </c>
       <c r="E10" t="inlineStr">
         <is>
           <t>no</t>
@@ -676,46 +704,54 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>youth_officers_performance_evaluation_page_8</t>
+          <t>collaboration_skills</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Decimal</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr"/>
+          <t>How would you rate the youth officer's ability to work with colleagues and other departments?</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Select all that apply</t>
+        </is>
+      </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>youth_officers_performance_evaluation_page_9</t>
+          <t>time_management</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Email</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr"/>
+          <t>How would you rate the youth officer's time management skills?</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Rate on a scale of 1-5</t>
+        </is>
+      </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -727,15 +763,19 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>youth_officers_performance_evaluation_page_10</t>
+          <t>tasks_completed</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Phone</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr"/>
+          <t>What is the number of tasks completed within deadlines?</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Enter number</t>
+        </is>
+      </c>
       <c r="E13" t="inlineStr">
         <is>
           <t>no</t>
@@ -745,20 +785,24 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>youth_officers_performance_evaluation_page_11</t>
+          <t>problem_solving</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Select One</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr"/>
+          <t>How well do you rate the youth officer's problem-solving skills?</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Select all that apply</t>
+        </is>
+      </c>
       <c r="E14" t="inlineStr">
         <is>
           <t>yes</t>
@@ -768,322 +812,27 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>youth_officers_performance_evaluation_page_12</t>
+          <t>suggestions_for_improvement</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Select Multiple</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr"/>
+          <t>Are there any suggestions or areas for improvement for the youth officer?</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Enter text</t>
+        </is>
+      </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>youth_officers_performance_evaluation_page_13</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Select One</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>youth_officers_performance_evaluation_page_14</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Select Multiple</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>youth_officers_performance_evaluation_page_15</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Select One</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>youth_officers_performance_evaluation_page_16</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Select Multiple</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>youth_officers_performance_evaluation_page_17</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Select One</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>youth_officers_performance_evaluation_page_18</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Select Multiple</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>youth_officers_performance_evaluation_page_19</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Select One</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>youth_officers_performance_evaluation_page_20</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Select Multiple</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>youth_officers_performance_evaluation_page_21</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Select One</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>youth_officers_performance_evaluation_page_22</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Select Multiple</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>youth_officers_performance_evaluation_page_23</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Select One</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>youth_officers_performance_evaluation_page_24</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Select Multiple</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>youth_officers_performance_evaluation_page_25</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Select One</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
     </row>
@@ -1098,12 +847,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C35"/>
+  <dimension ref="A1:C28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="50" customWidth="1" min="1" max="1"/>
-    <col width="6" customWidth="1" min="2" max="2"/>
-    <col width="7" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="11" customWidth="1" min="2" max="2"/>
+    <col width="11" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1126,578 +875,459 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>youth_officers_performance_evaluation_page_2_choices</t>
+          <t>communication_skills_choices</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>excellent</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Excellent</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>youth_officers_performance_evaluation_page_2_choices</t>
+          <t>communication_skills_choices</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>good</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Good</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>youth_officers_performance_evaluation_page_3_choices</t>
+          <t>communication_skills_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>fair</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Fair</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>youth_officers_performance_evaluation_page_3_choices</t>
+          <t>communication_skills_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>poor</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Poor</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>youth_officers_performance_evaluation_page_11_choices</t>
+          <t>communication_skills_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>very_poor</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Very Poor</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>youth_officers_performance_evaluation_page_11_choices</t>
+          <t>leadership_skills_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>excellent</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Excellent</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>youth_officers_performance_evaluation_page_12_choices</t>
+          <t>leadership_skills_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>good</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Good</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>youth_officers_performance_evaluation_page_12_choices</t>
+          <t>leadership_skills_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>fair</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Fair</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>youth_officers_performance_evaluation_page_13_choices</t>
+          <t>leadership_skills_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>poor</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Poor</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>youth_officers_performance_evaluation_page_13_choices</t>
+          <t>leadership_skills_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>very_poor</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Very Poor</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>youth_officers_performance_evaluation_page_14_choices</t>
+          <t>report_submission_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>excellent</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Excellent</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>youth_officers_performance_evaluation_page_14_choices</t>
+          <t>report_submission_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>good</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Good</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>youth_officers_performance_evaluation_page_15_choices</t>
+          <t>report_submission_choices</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>fair</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Fair</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>youth_officers_performance_evaluation_page_15_choices</t>
+          <t>report_submission_choices</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>poor</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Poor</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>youth_officers_performance_evaluation_page_16_choices</t>
+          <t>collaboration_skills_choices</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>excellent</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Excellent</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>youth_officers_performance_evaluation_page_16_choices</t>
+          <t>collaboration_skills_choices</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>good</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Good</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>youth_officers_performance_evaluation_page_17_choices</t>
+          <t>collaboration_skills_choices</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>fair</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Fair</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>youth_officers_performance_evaluation_page_17_choices</t>
+          <t>collaboration_skills_choices</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>poor</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Poor</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>youth_officers_performance_evaluation_page_18_choices</t>
+          <t>time_management_choices</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>excellent</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Excellent</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>youth_officers_performance_evaluation_page_18_choices</t>
+          <t>time_management_choices</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>good</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Good</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>youth_officers_performance_evaluation_page_19_choices</t>
+          <t>time_management_choices</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>fair</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Fair</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>youth_officers_performance_evaluation_page_19_choices</t>
+          <t>time_management_choices</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>poor</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Poor</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>youth_officers_performance_evaluation_page_20_choices</t>
+          <t>time_management_choices</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>very_poor</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Very Poor</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>youth_officers_performance_evaluation_page_20_choices</t>
+          <t>problem_solving_choices</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>excellent</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Excellent</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>youth_officers_performance_evaluation_page_21_choices</t>
+          <t>problem_solving_choices</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>good</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Good</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>youth_officers_performance_evaluation_page_21_choices</t>
+          <t>problem_solving_choices</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>fair</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Fair</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>youth_officers_performance_evaluation_page_22_choices</t>
+          <t>problem_solving_choices</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>poor</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>youth_officers_performance_evaluation_page_22_choices</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>youth_officers_performance_evaluation_page_23_choices</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>youth_officers_performance_evaluation_page_23_choices</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>youth_officers_performance_evaluation_page_24_choices</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>youth_officers_performance_evaluation_page_24_choices</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>youth_officers_performance_evaluation_page_25_choices</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>youth_officers_performance_evaluation_page_25_choices</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>No</t>
+          <t>Poor</t>
         </is>
       </c>
     </row>
